--- a/business_forms/037_social_media_engagement_audit_form--business_forms.xlsx
+++ b/business_forms/037_social_media_engagement_audit_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1106,34 +1106,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>social_media_platform_choices</t>
+          <t>engagement_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>snapchat</t>
+          <t>posts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>Posts</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>social_media_platform_choices</t>
+          <t>engagement_type_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>snapchat</t>
+          <t>stories</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>Stories</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>posts</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Posts</t>
+          <t>Videos</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>stories</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stories</t>
+          <t>Comments</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>messages</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Videos</t>
+          <t>Messages</t>
         </is>
       </c>
     </row>
@@ -1196,46 +1196,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>reviews</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Reviews</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>engagement_type_choices</t>
+          <t>engagement_level_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>messages</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Messages</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>engagement_type_choices</t>
+          <t>engagement_level_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>reviews</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1264,44 +1264,10 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>engagement_level_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>engagement_level_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>very_high</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
